--- a/2LabsToGo-Eco-Hardware/Electronics/electronic-parts-lists.xlsx
+++ b/2LabsToGo-Eco-Hardware/Electronics/electronic-parts-lists.xlsx
@@ -1,28 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wschwack\JLUbox\2LabsToGo\Mainboard\doku_2LabsToGo_Electronic\Mainboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wschwack\Nextcloud\2LabsToGo\Mainboard\doku_2LabsToGo_Electronic\Finale-Listen_280326\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBCA6C6-A7F4-47D2-8C1A-ABC91E448225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="5910"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mainboard" sheetId="1" r:id="rId1"/>
-    <sheet name="status led board" sheetId="2" r:id="rId2"/>
-    <sheet name="UV led boards" sheetId="3" r:id="rId3"/>
-    <sheet name="plugs and cables" sheetId="4" r:id="rId4"/>
+    <sheet name="mainboard-smd" sheetId="5" r:id="rId2"/>
+    <sheet name="status led board" sheetId="2" r:id="rId3"/>
+    <sheet name="UV led boards" sheetId="3" r:id="rId4"/>
+    <sheet name="plugs and cables" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="341">
   <si>
     <t>ID</t>
   </si>
@@ -162,9 +177,6 @@
     <t>R84</t>
   </si>
   <si>
-    <t>I2C_3,I2C_1,I2C_2,DHT1</t>
-  </si>
-  <si>
     <t>SOD-323_11396254</t>
   </si>
   <si>
@@ -609,9 +621,6 @@
     <t>69145-206LF</t>
   </si>
   <si>
-    <t>69145-208LF</t>
-  </si>
-  <si>
     <t>IDSD-20-D-02.00</t>
   </si>
   <si>
@@ -702,33 +711,6 @@
     <t>plug external port</t>
   </si>
   <si>
-    <t>Pluggable Terminal Blocks 5 Pos 3.81mm pitch Plug 28-16 AWG Screw</t>
-  </si>
-  <si>
-    <t>Pluggable Terminal Blocks 7 Pos 3.81mm pitch Plug 28-16 AWG Screw</t>
-  </si>
-  <si>
-    <t>Pluggable Terminal Blocks 2 Pos 3.81mm pitch Plug 28-16 AWG Screw</t>
-  </si>
-  <si>
-    <t>Pluggable Terminal Blocks 4 Pos 5.08mm pitch Plug 24-12 AWG Screw</t>
-  </si>
-  <si>
-    <t>Ribbon Cables / IDC Cables Slim Body Double-Row IDC Socket Assemblies</t>
-  </si>
-  <si>
-    <t>Ribbon Cables / IDC Cables Slim Body Single-Row IDC Socket Assemblies</t>
-  </si>
-  <si>
-    <t>Headers &amp; Wire Housings 2X3 POS SHUNT</t>
-  </si>
-  <si>
-    <t>Headers &amp; Wire Housings JUMPER LOW D/R</t>
-  </si>
-  <si>
-    <t>Pluggable Terminal Blocks 6 Pos 3.5mm pitch Plug 28-16 AWG Screw</t>
-  </si>
-  <si>
     <t>CHIP-LED0805</t>
   </si>
   <si>
@@ -939,9 +921,6 @@
     <t>Headers &amp; Wire Housings 12P DR UNSHRD HRD TIN OVER NI</t>
   </si>
   <si>
-    <t>see 23</t>
-  </si>
-  <si>
     <t>5x2</t>
   </si>
   <si>
@@ -1005,9 +984,6 @@
     <t>SMD3535</t>
   </si>
   <si>
-    <t>UV 365 nm LED, Inolux IN-C33CTNU2</t>
-  </si>
-  <si>
     <t>IN-C33CTNU2</t>
   </si>
   <si>
@@ -1030,12 +1006,66 @@
   </si>
   <si>
     <t>AVR AVR® ATmega Mikrocontroller IC 8-Bit 16MHz 256KB (128K x 16) FLASH 100-TQFP (14x14)</t>
+  </si>
+  <si>
+    <t>surface mount</t>
+  </si>
+  <si>
+    <t>I2C_3,I2C_1,I2C_2</t>
+  </si>
+  <si>
+    <t>DHT1?</t>
+  </si>
+  <si>
+    <t>Extern buttom??</t>
+  </si>
+  <si>
+    <t>see 21</t>
+  </si>
+  <si>
+    <t>69145-108LF</t>
+  </si>
+  <si>
+    <t>8 (2 x 4) Position Shunt Connector Black Open Top 0.100" (2.54mm) Gold or Gold, GXT™</t>
+  </si>
+  <si>
+    <t>6 (2 x 3) Position Shunt Connector Black Open Top 0.100" (2.54mm) Gold or Gold, GXT™</t>
+  </si>
+  <si>
+    <t>40 Position Cable Assembly Rectangular Socket to Socket 0.167' (50.80mm, 2.00")</t>
+  </si>
+  <si>
+    <t>14 Position Cable Assembly Rectangular Socket to Socket</t>
+  </si>
+  <si>
+    <t>TJ0451560000G</t>
+  </si>
+  <si>
+    <t>Amphenol Anytek</t>
+  </si>
+  <si>
+    <t>4 Position Terminal Block Plug, Female Sockets 0.200" (5.08mm) 180° Free Hanging (In-Line)</t>
+  </si>
+  <si>
+    <t>5 Position Terminal Block Plug, Female Sockets 0.150" (3.81mm) 180° Free Hanging (In-Line)</t>
+  </si>
+  <si>
+    <t>7 Position Terminal Block Plug, Female Sockets 0.150" (3.81mm) 180° Free Hanging (In-Line)</t>
+  </si>
+  <si>
+    <t>2 Position Terminal Block Plug, Female Sockets 0.150" (3.81mm) 180° Free Hanging (In-Line)</t>
+  </si>
+  <si>
+    <t>6 Position Terminal Block Plug, Female Sockets 0.138" (3.50mm) 180° Free Hanging (In-Line)</t>
+  </si>
+  <si>
+    <t>Ultraviolet (UV) Emitter 365nm ~ 370nm 3.5V 1A 120° 1414 (3535 Metric)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1197,7 +1227,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1377,8 +1407,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1493,6 +1529,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1538,7 +1589,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1552,7 +1603,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1563,16 +1613,33 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1629,6 +1696,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>56027</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>114545</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C51CA06-B92D-F4C4-B443-2182A43F622B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14068425" y="5429250"/>
+          <a:ext cx="5601482" cy="1752845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1893,58 +2009,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W79"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="76.140625" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="76.109375" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B1" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>222</v>
+      <c r="H2" s="10" t="s">
+        <v>220</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1961,29 +2077,29 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>112</v>
+        <v>228</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>13</v>
       </c>
       <c r="I3" s="2"/>
@@ -2001,29 +2117,29 @@
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>112</v>
+        <v>229</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>33</v>
       </c>
       <c r="I4" s="2"/>
@@ -2041,29 +2157,29 @@
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>112</v>
+        <v>230</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>2</v>
       </c>
       <c r="I5" s="2"/>
@@ -2081,7 +2197,7 @@
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -2089,21 +2205,21 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>112</v>
+        <v>231</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>2</v>
       </c>
       <c r="I6" s="2"/>
@@ -2121,29 +2237,29 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>112</v>
+        <v>232</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>2</v>
       </c>
       <c r="I7" s="2"/>
@@ -2161,29 +2277,29 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>112</v>
+        <v>233</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>8</v>
       </c>
       <c r="I8" s="2"/>
@@ -2201,29 +2317,29 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>112</v>
+        <v>234</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>2</v>
       </c>
       <c r="I9" s="2"/>
@@ -2241,29 +2357,29 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>112</v>
+        <v>235</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="8">
+        <v>49</v>
+      </c>
+      <c r="H10" s="7">
         <v>1</v>
       </c>
       <c r="I10" s="2"/>
@@ -2281,29 +2397,29 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>1</v>
       </c>
       <c r="I11" s="2"/>
@@ -2321,7 +2437,7 @@
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -2329,21 +2445,21 @@
         <v>27</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>112</v>
+        <v>237</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>1</v>
       </c>
       <c r="I12" s="2"/>
@@ -2361,29 +2477,29 @@
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>112</v>
+        <v>238</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <v>6</v>
       </c>
       <c r="I13" s="2"/>
@@ -2401,29 +2517,29 @@
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>112</v>
+        <v>239</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="8">
+        <v>46</v>
+      </c>
+      <c r="H14" s="7">
         <v>2</v>
       </c>
       <c r="I14" s="2"/>
@@ -2441,29 +2557,29 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <v>3</v>
       </c>
       <c r="I15" s="2"/>
@@ -2481,29 +2597,29 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>2</v>
       </c>
       <c r="I16" s="2"/>
@@ -2521,29 +2637,29 @@
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>1</v>
       </c>
       <c r="I17" s="2"/>
@@ -2561,29 +2677,29 @@
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>2</v>
       </c>
       <c r="I18" s="2"/>
@@ -2601,7 +2717,7 @@
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2609,21 +2725,21 @@
         <v>20</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>2</v>
       </c>
       <c r="I19" s="2"/>
@@ -2641,29 +2757,29 @@
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>112</v>
+        <v>245</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H20" s="8">
+        <v>131</v>
+      </c>
+      <c r="H20" s="7">
         <v>2</v>
       </c>
       <c r="I20" s="2"/>
@@ -2681,29 +2797,29 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>112</v>
+        <v>246</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H21" s="8">
+        <v>131</v>
+      </c>
+      <c r="H21" s="7">
         <v>3</v>
       </c>
       <c r="I21" s="2"/>
@@ -2721,29 +2837,29 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>112</v>
+        <v>247</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H22" s="8">
+        <v>131</v>
+      </c>
+      <c r="H22" s="7">
         <v>1</v>
       </c>
       <c r="I22" s="2"/>
@@ -2761,7 +2877,7 @@
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2769,21 +2885,21 @@
         <v>4</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <v>1</v>
       </c>
       <c r="I23" s="2"/>
@@ -2801,29 +2917,29 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H24" s="8">
+      <c r="H24" s="7">
         <v>7</v>
       </c>
       <c r="I24" s="2"/>
@@ -2841,7 +2957,7 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2849,21 +2965,21 @@
         <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>1</v>
       </c>
       <c r="I25" s="2"/>
@@ -2881,7 +2997,7 @@
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2889,21 +3005,21 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>112</v>
+        <v>251</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="7">
         <v>13</v>
       </c>
       <c r="I26" s="2"/>
@@ -2921,7 +3037,7 @@
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2929,21 +3045,21 @@
         <v>40</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>112</v>
+        <v>252</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="7">
         <v>2</v>
       </c>
       <c r="I27" s="2"/>
@@ -2961,29 +3077,29 @@
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>112</v>
+        <v>253</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="7">
         <v>9</v>
       </c>
       <c r="I28" s="2"/>
@@ -3001,29 +3117,29 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>112</v>
+        <v>254</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="7">
         <v>16</v>
       </c>
       <c r="I29" s="2"/>
@@ -3041,29 +3157,29 @@
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
     </row>
-    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>112</v>
+        <v>255</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="7">
         <v>17</v>
       </c>
       <c r="I30" s="2"/>
@@ -3081,29 +3197,29 @@
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>112</v>
+        <v>256</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="7">
         <v>4</v>
       </c>
       <c r="I31" s="2"/>
@@ -3121,7 +3237,7 @@
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -3129,21 +3245,21 @@
         <v>18</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>112</v>
+        <v>257</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="7">
         <v>3</v>
       </c>
       <c r="I32" s="2"/>
@@ -3161,29 +3277,29 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>112</v>
+        <v>258</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="7">
         <v>11</v>
       </c>
       <c r="I33" s="2"/>
@@ -3201,29 +3317,29 @@
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>112</v>
+        <v>259</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <v>1</v>
       </c>
       <c r="I34" s="2"/>
@@ -3241,7 +3357,7 @@
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -3249,21 +3365,21 @@
         <v>45</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>112</v>
+        <v>260</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="7">
         <v>1</v>
       </c>
       <c r="I35" s="2"/>
@@ -3281,29 +3397,29 @@
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>112</v>
+        <v>261</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="7">
         <v>1</v>
       </c>
       <c r="I36" s="2"/>
@@ -3321,29 +3437,29 @@
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>112</v>
+        <v>262</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="7">
         <v>1</v>
       </c>
       <c r="I37" s="2"/>
@@ -3361,7 +3477,7 @@
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -3369,21 +3485,21 @@
         <v>39</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>112</v>
+        <v>263</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="7">
         <v>9</v>
       </c>
       <c r="I38" s="2"/>
@@ -3401,7 +3517,7 @@
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -3409,21 +3525,21 @@
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H39" s="8">
+      <c r="H39" s="7">
         <v>4</v>
       </c>
       <c r="I39" s="2"/>
@@ -3441,7 +3557,7 @@
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -3452,18 +3568,18 @@
         <v>22</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>112</v>
+        <v>265</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H40" s="8">
+        <v>153</v>
+      </c>
+      <c r="H40" s="7">
         <v>2</v>
       </c>
       <c r="I40" s="2"/>
@@ -3481,29 +3597,29 @@
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>112</v>
+        <v>266</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H41" s="8">
+        <v>153</v>
+      </c>
+      <c r="H41" s="7">
         <v>3</v>
       </c>
       <c r="I41" s="2"/>
@@ -3521,29 +3637,29 @@
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H42" s="8">
+      <c r="H42" s="7">
         <v>1</v>
       </c>
       <c r="I42" s="2"/>
@@ -3561,7 +3677,7 @@
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -3572,18 +3688,18 @@
         <v>42</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>112</v>
+        <v>322</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H43" s="8">
+        <v>216</v>
+      </c>
+      <c r="H43" s="7">
         <v>1</v>
       </c>
       <c r="I43" s="2"/>
@@ -3601,7 +3717,7 @@
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -3612,18 +3728,18 @@
         <v>24</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>112</v>
+        <v>268</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H44" s="8">
+        <v>179</v>
+      </c>
+      <c r="H44" s="7">
         <v>1</v>
       </c>
       <c r="I44" s="2"/>
@@ -3641,14 +3757,31 @@
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="8"/>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="6">
+        <v>74477020</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" t="s">
+        <v>273</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H45" s="7">
+        <v>1</v>
+      </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -3664,17 +3797,31 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="6">
+        <v>744770222</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="7">
+        <v>1</v>
+      </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -3690,31 +3837,14 @@
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>222</v>
-      </c>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="7"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -3730,31 +3860,17 @@
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>1</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" t="s">
-        <v>280</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="8">
-        <v>3</v>
-      </c>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -3770,30 +3886,30 @@
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>2</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E49" t="s">
-        <v>281</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H49" s="8">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>1</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>220</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
@@ -3810,30 +3926,30 @@
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
+        <v>1</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" t="s">
+        <v>269</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="7">
         <v>3</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E50" t="s">
-        <v>282</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H50" s="8">
-        <v>1</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -3849,31 +3965,30 @@
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
-        <v>283</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>113</v>
+        <v>270</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H51" s="8">
+        <v>146</v>
+      </c>
+      <c r="H51" s="7">
         <v>1</v>
       </c>
       <c r="I51" s="2"/>
@@ -3891,29 +4006,29 @@
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>193</v>
+        <v>50</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="E52" t="s">
-        <v>94</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>113</v>
+        <v>271</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H52" s="8">
+        <v>51</v>
+      </c>
+      <c r="H52" s="7">
         <v>1</v>
       </c>
       <c r="I52" s="2"/>
@@ -3930,30 +4045,31 @@
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W52" s="2"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C53" s="6">
-        <v>74477020</v>
+        <v>80</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E53" t="s">
-        <v>284</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>113</v>
+        <v>272</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H53" s="8">
+        <v>81</v>
+      </c>
+      <c r="H53" s="7">
         <v>1</v>
       </c>
       <c r="I53" s="2"/>
@@ -3971,29 +4087,29 @@
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" s="6">
-        <v>744770222</v>
+        <v>65</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E54" t="s">
-        <v>285</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>113</v>
+        <v>93</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H54" s="8">
+        <v>66</v>
+      </c>
+      <c r="H54" s="7">
         <v>1</v>
       </c>
       <c r="I54" s="2"/>
@@ -4011,29 +4127,29 @@
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="E55" t="s">
-        <v>286</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>113</v>
+        <v>275</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="7">
         <v>1</v>
       </c>
       <c r="I55" s="2"/>
@@ -4050,29 +4166,29 @@
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="E56" t="s">
-        <v>287</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>113</v>
+        <v>276</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="7">
         <v>1</v>
       </c>
       <c r="I56" s="2"/>
@@ -4090,29 +4206,29 @@
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E57" t="s">
-        <v>288</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>113</v>
+        <v>277</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="7">
         <v>2</v>
       </c>
       <c r="I57" s="2"/>
@@ -4130,29 +4246,29 @@
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E58" t="s">
-        <v>289</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>113</v>
+        <v>278</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="7">
         <v>3</v>
       </c>
       <c r="I58" s="2"/>
@@ -4170,29 +4286,29 @@
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E59" t="s">
-        <v>290</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>113</v>
+        <v>279</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="7">
         <v>1</v>
       </c>
       <c r="I59" s="2"/>
@@ -4210,29 +4326,29 @@
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E60" t="s">
-        <v>291</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>113</v>
+        <v>280</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="7">
         <v>1</v>
       </c>
       <c r="I60" s="2"/>
@@ -4250,29 +4366,29 @@
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E61" t="s">
+        <v>92</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E61" t="s">
-        <v>93</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H61" s="8">
+      <c r="H61" s="7">
         <v>1</v>
       </c>
       <c r="I61" s="2"/>
@@ -4290,29 +4406,29 @@
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E62" t="s">
+        <v>281</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E62" t="s">
-        <v>292</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H62" s="8">
+      <c r="H62" s="7">
         <v>1</v>
       </c>
       <c r="I62" s="2"/>
@@ -4330,30 +4446,30 @@
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E63" t="s">
-        <v>293</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>113</v>
+        <v>282</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H63" s="8" t="s">
-        <v>306</v>
+      <c r="H63" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4370,29 +4486,29 @@
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C64" s="4">
         <v>1757268</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E64" t="s">
-        <v>294</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>113</v>
+        <v>283</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H64" s="8">
+        <v>91</v>
+      </c>
+      <c r="H64" s="7">
         <v>1</v>
       </c>
       <c r="I64" s="2"/>
@@ -4410,9 +4526,9 @@
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>43</v>
@@ -4421,18 +4537,18 @@
         <v>1803426</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E65" t="s">
-        <v>295</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>113</v>
+        <v>284</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H65" s="8">
+      <c r="H65" s="7">
         <v>5</v>
       </c>
       <c r="I65" s="2"/>
@@ -4450,29 +4566,29 @@
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C66" s="4">
         <v>1803455</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E66" t="s">
-        <v>296</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>113</v>
+        <v>285</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="H66" s="8">
+        <v>201</v>
+      </c>
+      <c r="H66" s="7">
         <v>1</v>
       </c>
       <c r="I66" s="2"/>
@@ -4490,29 +4606,29 @@
       <c r="U66" s="2"/>
       <c r="V66" s="2"/>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C67" s="4">
         <v>1803471</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E67" t="s">
-        <v>297</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>113</v>
+        <v>286</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="H67" s="8">
+        <v>202</v>
+      </c>
+      <c r="H67" s="7">
         <v>1</v>
       </c>
       <c r="I67" s="2"/>
@@ -4530,9 +4646,9 @@
       <c r="U67" s="2"/>
       <c r="V67" s="2"/>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>29</v>
@@ -4541,18 +4657,18 @@
         <v>1876301</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E68" t="s">
-        <v>298</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>113</v>
+        <v>287</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H68" s="8">
+      <c r="H68" s="7">
         <v>1</v>
       </c>
       <c r="I68" s="2"/>
@@ -4570,29 +4686,29 @@
       <c r="U68" s="2"/>
       <c r="V68" s="2"/>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="E69" t="s">
-        <v>299</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>113</v>
+        <v>288</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H69" s="8">
+      <c r="H69" s="7">
         <v>1</v>
       </c>
       <c r="I69" s="2"/>
@@ -4610,29 +4726,29 @@
       <c r="U69" s="2"/>
       <c r="V69" s="2"/>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>46</v>
+        <v>324</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E70" t="s">
-        <v>300</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>113</v>
+        <v>289</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H70" s="8">
+        <v>74</v>
+      </c>
+      <c r="H70" s="7">
         <v>3</v>
       </c>
       <c r="I70" s="2"/>
@@ -4650,24 +4766,24 @@
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="D71" s="2"/>
-      <c r="F71" s="8" t="s">
-        <v>113</v>
+      <c r="F71" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H71" s="8"/>
+        <v>197</v>
+      </c>
+      <c r="H71" s="7"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -4683,24 +4799,24 @@
       <c r="U71" s="2"/>
       <c r="V71" s="2"/>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D72" s="2"/>
+      <c r="F72" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D72" s="2"/>
-      <c r="F72" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H72" s="8"/>
+      <c r="H72" s="7"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -4716,24 +4832,24 @@
       <c r="U72" s="2"/>
       <c r="V72" s="2"/>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="D73" s="2"/>
-      <c r="F73" s="8" t="s">
-        <v>113</v>
+      <c r="F73" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H73" s="8"/>
+      <c r="H73" s="7"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -4749,29 +4865,29 @@
       <c r="U73" s="2"/>
       <c r="V73" s="2"/>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E74" t="s">
-        <v>301</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>113</v>
+        <v>290</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="H74" s="8">
+        <v>212</v>
+      </c>
+      <c r="H74" s="7">
         <v>1</v>
       </c>
       <c r="I74" s="2"/>
@@ -4789,29 +4905,29 @@
       <c r="U74" s="2"/>
       <c r="V74" s="2"/>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E75" t="s">
-        <v>302</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>113</v>
+        <v>291</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H75" s="8">
+        <v>198</v>
+      </c>
+      <c r="H75" s="7">
         <v>1</v>
       </c>
       <c r="I75" s="2"/>
@@ -4829,29 +4945,29 @@
       <c r="U75" s="2"/>
       <c r="V75" s="2"/>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E76" t="s">
-        <v>303</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>113</v>
+        <v>292</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="H76" s="8">
+        <v>199</v>
+      </c>
+      <c r="H76" s="7">
         <v>1</v>
       </c>
       <c r="I76" s="2"/>
@@ -4869,29 +4985,29 @@
       <c r="U76" s="2"/>
       <c r="V76" s="2"/>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E77" t="s">
-        <v>304</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>113</v>
+        <v>293</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H77" s="8">
+        <v>200</v>
+      </c>
+      <c r="H77" s="7">
         <v>1</v>
       </c>
       <c r="I77" s="2"/>
@@ -4909,358 +5025,2183 @@
       <c r="U77" s="2"/>
       <c r="V77" s="2"/>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="2"/>
+      <c r="B78" s="20" t="s">
+        <v>325</v>
+      </c>
       <c r="S78" s="2"/>
       <c r="T78" s="2"/>
       <c r="U78" s="2"/>
       <c r="V78" s="2"/>
     </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B79" s="20" t="s">
+        <v>326</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="K48:K60">
-    <sortCondition ref="K48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K50:K60">
+    <sortCondition ref="K50"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B48:H48"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D51" r:id="rId1" display="https://www.mouser.de/manufacturer/same-sky/"/>
+    <hyperlink ref="D53" r:id="rId1" display="https://www.mouser.de/manufacturer/same-sky/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6706DD-0D58-47E0-B790-EC5089FE7B06}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="76.109375" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="F2" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="16">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="16">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="14">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="16">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="14">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="16">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="16">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
+        <v>6</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="16">
+        <v>8</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="14">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="16">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="16">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="16">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="16">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="16">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="16">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" s="16">
+        <v>3</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="16">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="16">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
+        <v>16</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="16">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="14">
+        <v>17</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="H19" s="16">
+        <v>2</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="14">
+        <v>18</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="16">
+        <v>2</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="14">
+        <v>19</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H21" s="16">
+        <v>3</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="14">
+        <v>20</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="16">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="14">
+        <v>21</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" s="16">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="14">
+        <v>22</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="16">
+        <v>7</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="14">
+        <v>23</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="16">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" s="14">
+        <v>24</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="16">
+        <v>13</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" s="14">
+        <v>25</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="16">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
+        <v>26</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="16">
+        <v>9</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" s="14">
+        <v>27</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" s="16">
+        <v>16</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+    </row>
+    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="14">
+        <v>28</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="16">
+        <v>17</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" s="14">
+        <v>29</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="D31" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="16">
+        <v>4</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" s="14">
+        <v>30</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="16">
+        <v>3</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="14">
+        <v>31</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" s="16">
+        <v>11</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
+        <v>32</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" s="16">
         <v>1</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
+        <v>33</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" s="16">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="E3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" t="s">
-        <v>235</v>
-      </c>
-      <c r="H3" s="9">
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A36" s="14">
+        <v>34</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" s="16">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="14">
+        <v>35</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H37" s="16">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="14">
+        <v>36</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38" s="16">
+        <v>9</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" s="14">
+        <v>37</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" s="16">
+        <v>4</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" s="14">
+        <v>38</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="H40" s="16">
+        <v>2</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="14">
+        <v>39</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="H41" s="16">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C4" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" t="s">
-        <v>235</v>
-      </c>
-      <c r="H4" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C5" t="s">
-        <v>309</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="E5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" t="s">
-        <v>235</v>
-      </c>
-      <c r="H5" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="14">
+        <v>40</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="16">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" s="14">
+        <v>41</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="H43" s="16">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A44" s="14">
+        <v>42</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="H44" s="16">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" s="14">
+        <v>43</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="19">
+        <v>74477020</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="E45" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H45" s="16">
         <v>1</v>
       </c>
+      <c r="S45" s="2"/>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A46" s="14">
+        <v>44</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="19">
+        <v>744770222</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="16">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:H6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="2"/>
+    <col min="2" max="2" width="39.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H3" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H4" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
     <col min="4" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="F3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="9">
+        <v>304</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D4" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="F4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="I4" s="9">
+        <v>312</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="I4" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" t="s">
         <v>320</v>
       </c>
-      <c r="D8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" t="s">
-        <v>333</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="I8" s="9">
+        <v>309</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C9" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E9" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="F9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="I9" s="9">
+        <v>340</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="I9" s="8">
         <v>4</v>
       </c>
     </row>
@@ -5269,226 +7210,226 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="68" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="72.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="5" max="5" width="72.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="G2" s="10"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F3" s="9">
+        <v>330</v>
+      </c>
+      <c r="F3" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>195</v>
+        <v>328</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F4" s="9">
+        <v>329</v>
+      </c>
+      <c r="F4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F5" s="9">
+        <v>331</v>
+      </c>
+      <c r="F5" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F6" s="9">
+        <v>332</v>
+      </c>
+      <c r="F6" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1757035</v>
+        <v>223</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>333</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>148</v>
+        <v>334</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F7" s="9">
+        <v>335</v>
+      </c>
+      <c r="F7" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4">
         <v>1803604</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F8" s="9">
+        <v>336</v>
+      </c>
+      <c r="F8" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C9" s="4">
         <v>1803620</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" s="9">
+        <v>337</v>
+      </c>
+      <c r="F9" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C10" s="4">
         <v>1803578</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F10" s="9">
+        <v>338</v>
+      </c>
+      <c r="F10" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C11" s="4">
         <v>1840405</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11" s="9">
+        <v>339</v>
+      </c>
+      <c r="F11" s="8">
         <v>1</v>
       </c>
     </row>
